--- a/ejemplos/Importar-correctos.xlsx
+++ b/ejemplos/Importar-correctos.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Productos OEM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Equivalencias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,10 +26,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -435,7 +433,7 @@
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
   </cols>
@@ -504,11 +502,13 @@
           <t>Producto</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>6</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Unidad</t>
+        </is>
       </c>
       <c r="G2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -538,12 +538,6 @@
           <t>Producto</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>12</v>
-      </c>
-      <c r="G3" t="n">
-        <v>24</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>Activo</t>
@@ -574,8 +568,10 @@
           <t>Presentación</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>4</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Inner</t>
+        </is>
       </c>
       <c r="G4" t="n">
         <v>8</v>
@@ -605,14 +601,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Producto</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
+          <t>Presentación</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Caja máster</t>
+        </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -644,11 +642,13 @@
           <t>Presentación</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>2</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pallet</t>
+        </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>

--- a/ejemplos/Importar-correctos.xlsx
+++ b/ejemplos/Importar-correctos.xlsx
@@ -55,11 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +432,7 @@
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -494,8 +495,10 @@
           <t>GS1</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>7501031311309</v>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>7501234567893</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -530,8 +533,10 @@
           <t>GS1</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>7501234567890</v>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>07501234567893</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -558,7 +563,7 @@
           <t>No GS1</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>NGK-IR-4544</t>
         </is>
@@ -596,8 +601,10 @@
           <t>GS1</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>7502208841236</v>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>036000291452</t>
+        </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -632,7 +639,7 @@
           <t>No GS1</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>TMK-HA590210</t>
         </is>

--- a/ejemplos/Importar-correctos.xlsx
+++ b/ejemplos/Importar-correctos.xlsx
@@ -442,7 +442,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>Código</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">

--- a/ejemplos/Importar-correctos.xlsx
+++ b/ejemplos/Importar-correctos.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Equivalencias" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Carga_Equivalencias" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
